--- a/staff_forms/004_overtime_authorization_form--staff_forms.xlsx
+++ b/staff_forms/004_overtime_authorization_form--staff_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'regular',_'label':_'regular'}</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Regular', 'label': 'Regular'}</t>
+          <t>Regular</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'double',_'label':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Double', 'label': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'triple',_'label':_'triple'}</t>
+          <t>triple</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Triple', 'label': 'Triple'}</t>
+          <t>Triple</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'manager',_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Manager', 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'team_lead',_'label':_'team_lead'}</t>
+          <t>team_lead</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Team Lead', 'label': 'Team Lead'}</t>
+          <t>Team Lead</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'department_head',_'label':_'department_head'}</t>
+          <t>department_head</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Department Head', 'label': 'Department Head'}</t>
+          <t>Department Head</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'manager',_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Manager', 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'team_lead',_'label':_'team_lead'}</t>
+          <t>team_lead</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Team Lead', 'label': 'Team Lead'}</t>
+          <t>Team Lead</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'department_head',_'label':_'department_head'}</t>
+          <t>department_head</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Department Head', 'label': 'Department Head'}</t>
+          <t>Department Head</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'approved',_'label':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Approved', 'label': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'pending',_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Pending', 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'denied',_'label':_'denied'}</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Denied', 'label': 'Denied'}</t>
+          <t>Denied</t>
         </is>
       </c>
     </row>
